--- a/Voting_Results_WA/Legislature Members 2026 version.xlsx
+++ b/Voting_Results_WA/Legislature Members 2026 version.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lians\OneDrive\Desktop\Halmo\Initial GIS Testing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lians\git\dwbr-website\Voting_Results_WA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD850E18-0C2B-49A8-BB12-D6931C0BFD5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{88EC31C5-747B-4D6C-A7C1-B6FF201BD8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="1" xr2:uid="{7F02FFD5-302B-4432-BB31-9536D168D991}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="4" activeTab="5" xr2:uid="{7F02FFD5-302B-4432-BB31-9536D168D991}"/>
   </bookViews>
   <sheets>
     <sheet name="House 2026" sheetId="1" r:id="rId1"/>
     <sheet name="House Aggregate 2026" sheetId="4" r:id="rId2"/>
     <sheet name="Senate 2026" sheetId="2" r:id="rId3"/>
-    <sheet name="Pivot Table" sheetId="3" r:id="rId4"/>
+    <sheet name="Pivot Table 2025" sheetId="3" r:id="rId4"/>
+    <sheet name="House 2020" sheetId="5" r:id="rId5"/>
+    <sheet name="House Aggregate 2020" sheetId="10" r:id="rId6"/>
+    <sheet name="Senate 2020" sheetId="6" r:id="rId7"/>
+    <sheet name="Pivot Table 2020" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId9"/>
+    <pivotCache cacheId="5" r:id="rId10"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -64,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="382">
   <si>
     <t>District</t>
   </si>
@@ -910,6 +915,306 @@
   </si>
   <si>
     <t>2 Yea</t>
+  </si>
+  <si>
+    <t>Wilcox</t>
+  </si>
+  <si>
+    <t>J.T.</t>
+  </si>
+  <si>
+    <t>McCaslin</t>
+  </si>
+  <si>
+    <t>Bob</t>
+  </si>
+  <si>
+    <t>Shea</t>
+  </si>
+  <si>
+    <t>Ramos</t>
+  </si>
+  <si>
+    <t>Bill</t>
+  </si>
+  <si>
+    <t>Kretz</t>
+  </si>
+  <si>
+    <t>Maycumber</t>
+  </si>
+  <si>
+    <t>Jacquelin</t>
+  </si>
+  <si>
+    <t>Klippert</t>
+  </si>
+  <si>
+    <t>Brad</t>
+  </si>
+  <si>
+    <t>Smith</t>
+  </si>
+  <si>
+    <t>Norma</t>
+  </si>
+  <si>
+    <t>Hudgins</t>
+  </si>
+  <si>
+    <t>Zack</t>
+  </si>
+  <si>
+    <t>Mosbrucker</t>
+  </si>
+  <si>
+    <t>Gina</t>
+  </si>
+  <si>
+    <t>Chandler</t>
+  </si>
+  <si>
+    <t>Bruce</t>
+  </si>
+  <si>
+    <t>Jenkin</t>
+  </si>
+  <si>
+    <t>Kraft</t>
+  </si>
+  <si>
+    <t>Vicki</t>
+  </si>
+  <si>
+    <t>Hoff</t>
+  </si>
+  <si>
+    <t>Vick</t>
+  </si>
+  <si>
+    <t>Brandon</t>
+  </si>
+  <si>
+    <t>Blake</t>
+  </si>
+  <si>
+    <t>Debolt</t>
+  </si>
+  <si>
+    <t>Richard</t>
+  </si>
+  <si>
+    <t>Dolan</t>
+  </si>
+  <si>
+    <t>Appleton</t>
+  </si>
+  <si>
+    <t>Sherry</t>
+  </si>
+  <si>
+    <t>Chambers</t>
+  </si>
+  <si>
+    <t>Kelly</t>
+  </si>
+  <si>
+    <t>Caldier</t>
+  </si>
+  <si>
+    <t>Young</t>
+  </si>
+  <si>
+    <t>Kilduff</t>
+  </si>
+  <si>
+    <t>Christine</t>
+  </si>
+  <si>
+    <t>Kirby</t>
+  </si>
+  <si>
+    <t>Johnson</t>
+  </si>
+  <si>
+    <t>Pellicciotti</t>
+  </si>
+  <si>
+    <t>Irwin</t>
+  </si>
+  <si>
+    <t>Cody</t>
+  </si>
+  <si>
+    <t>Eileen</t>
+  </si>
+  <si>
+    <t>Tarleton</t>
+  </si>
+  <si>
+    <t>Gael</t>
+  </si>
+  <si>
+    <t>Pettigrew</t>
+  </si>
+  <si>
+    <t>Eric</t>
+  </si>
+  <si>
+    <t>Sells</t>
+  </si>
+  <si>
+    <t>Sutherland</t>
+  </si>
+  <si>
+    <t>Senn</t>
+  </si>
+  <si>
+    <t>Tana</t>
+  </si>
+  <si>
+    <t>Van Werven</t>
+  </si>
+  <si>
+    <t>Luanne</t>
+  </si>
+  <si>
+    <t>Chopp</t>
+  </si>
+  <si>
+    <t>Frank</t>
+  </si>
+  <si>
+    <t>Mead</t>
+  </si>
+  <si>
+    <t>Jared</t>
+  </si>
+  <si>
+    <t>Sullivan</t>
+  </si>
+  <si>
+    <t>Pat</t>
+  </si>
+  <si>
+    <t>Becker</t>
+  </si>
+  <si>
+    <t>Randi</t>
+  </si>
+  <si>
+    <t>Billig</t>
+  </si>
+  <si>
+    <t>Andy</t>
+  </si>
+  <si>
+    <t>Padden</t>
+  </si>
+  <si>
+    <t>Mullet</t>
+  </si>
+  <si>
+    <t>Brown</t>
+  </si>
+  <si>
+    <t>Hawkins</t>
+  </si>
+  <si>
+    <t>Judy</t>
+  </si>
+  <si>
+    <t>Honeyford</t>
+  </si>
+  <si>
+    <t>Maureen</t>
+  </si>
+  <si>
+    <t>Lynda</t>
+  </si>
+  <si>
+    <t>Rivers</t>
+  </si>
+  <si>
+    <t>Ann</t>
+  </si>
+  <si>
+    <t>Takko</t>
+  </si>
+  <si>
+    <t>Dean</t>
+  </si>
+  <si>
+    <t>Rolfes</t>
+  </si>
+  <si>
+    <t>Van De Wege</t>
+  </si>
+  <si>
+    <t>Zeiger</t>
+  </si>
+  <si>
+    <t>Hans</t>
+  </si>
+  <si>
+    <t>Randall</t>
+  </si>
+  <si>
+    <t>Darneille</t>
+  </si>
+  <si>
+    <t>Jeannie</t>
+  </si>
+  <si>
+    <t>O'Ban</t>
+  </si>
+  <si>
+    <t>Keiser</t>
+  </si>
+  <si>
+    <t>Karen</t>
+  </si>
+  <si>
+    <t>Nguyen</t>
+  </si>
+  <si>
+    <t>Sheldon</t>
+  </si>
+  <si>
+    <t>Tim</t>
+  </si>
+  <si>
+    <t>Carlyle</t>
+  </si>
+  <si>
+    <t>Reuven</t>
+  </si>
+  <si>
+    <t>McCoy</t>
+  </si>
+  <si>
+    <t>Ericksen</t>
+  </si>
+  <si>
+    <t>Doug</t>
+  </si>
+  <si>
+    <t>Hobbs</t>
+  </si>
+  <si>
+    <t>Frockt</t>
+  </si>
+  <si>
+    <t>Das</t>
+  </si>
+  <si>
+    <t>Mona</t>
+  </si>
+  <si>
+    <t>Kuderer</t>
+  </si>
+  <si>
+    <t>Patty</t>
   </si>
 </sst>
 </file>
@@ -917,12 +1222,26 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="000"/>
+    <numFmt numFmtId="164" formatCode="000"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF11734B"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFB10202"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -948,14 +1267,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -979,7 +1312,7 @@
     <worksheetSource ref="A1:E1048576" sheet="House 2026"/>
   </cacheSource>
   <cacheFields count="5">
-    <cacheField name="District" numFmtId="165">
+    <cacheField name="District" numFmtId="164">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="49" count="50">
         <n v="1"/>
         <n v="2"/>
@@ -1059,6 +1392,91 @@
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Li-An Song" refreshedDate="46155.705858564812" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="99" xr:uid="{396B6852-3AE1-4CC6-8330-820B6C930FA6}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:E1048576" sheet="House 2020"/>
+  </cacheSource>
+  <cacheFields count="5">
+    <cacheField name="District" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="49" count="50">
+        <n v="1"/>
+        <n v="2"/>
+        <n v="3"/>
+        <n v="4"/>
+        <n v="5"/>
+        <n v="6"/>
+        <n v="7"/>
+        <n v="8"/>
+        <n v="9"/>
+        <n v="10"/>
+        <n v="11"/>
+        <n v="12"/>
+        <n v="13"/>
+        <n v="14"/>
+        <n v="15"/>
+        <n v="16"/>
+        <n v="17"/>
+        <n v="18"/>
+        <n v="19"/>
+        <n v="20"/>
+        <n v="21"/>
+        <n v="22"/>
+        <n v="23"/>
+        <n v="24"/>
+        <n v="25"/>
+        <n v="26"/>
+        <n v="27"/>
+        <n v="28"/>
+        <n v="29"/>
+        <n v="30"/>
+        <n v="31"/>
+        <n v="32"/>
+        <n v="33"/>
+        <n v="34"/>
+        <n v="35"/>
+        <n v="36"/>
+        <n v="37"/>
+        <n v="38"/>
+        <n v="39"/>
+        <n v="40"/>
+        <n v="41"/>
+        <n v="42"/>
+        <n v="43"/>
+        <n v="44"/>
+        <n v="45"/>
+        <n v="46"/>
+        <n v="47"/>
+        <n v="48"/>
+        <n v="49"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Last" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="First" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Party" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Vote" numFmtId="0">
+      <sharedItems containsBlank="1" count="3">
+        <s v="Yea"/>
+        <s v="Nay"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="99">
   <r>
@@ -1757,8 +2175,706 @@
 </pivotCacheRecords>
 </file>
 
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="99">
+  <r>
+    <x v="0"/>
+    <s v="Duerr"/>
+    <s v="Davina"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="Kloba"/>
+    <s v="Shelley"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Barkis"/>
+    <s v="Andrew"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Wilcox"/>
+    <s v="J.T."/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="Ormsby"/>
+    <s v="Timm"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="Riccelli"/>
+    <s v="Marcus"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="McCaslin"/>
+    <s v="Bob"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="Shea"/>
+    <s v="Matt"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="Callan"/>
+    <s v="Lisa"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="Ramos"/>
+    <s v="Bill"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="Graham"/>
+    <s v="Jenny"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="Volz"/>
+    <s v="Mike"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <s v="Kretz"/>
+    <s v="Joel"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <s v="Maycumber"/>
+    <s v="Jacquelin"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="Boehnke"/>
+    <s v="Matt"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="Klippert"/>
+    <s v="Brad"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="Dye"/>
+    <s v="Mary"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="Schmick"/>
+    <s v="Joe"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="Paul"/>
+    <s v="Dave"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="Smith"/>
+    <s v="Norma"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <s v="Bergquist"/>
+    <s v="Steve"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <s v="Hudgins"/>
+    <s v="Zack"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <s v="Goehner"/>
+    <s v="Keith"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <s v="Steele"/>
+    <s v="Mike"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <s v="Dent"/>
+    <s v="Tom"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <s v="Ybarra"/>
+    <s v="Alex"/>
+    <s v="R"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <s v="Corry"/>
+    <s v="Chris"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <s v="Mosbrucker"/>
+    <s v="Gina"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <s v="Chandler"/>
+    <s v="Bruce"/>
+    <s v="R"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <s v="Dufault"/>
+    <s v="Jeremie"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <s v="Jenkin"/>
+    <s v="Bill"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <s v="Rude"/>
+    <s v="Skyler"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="16"/>
+    <s v="Harris"/>
+    <s v="Paul"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="16"/>
+    <s v="Kraft"/>
+    <s v="Vicki"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <s v="Hoff"/>
+    <s v="Larry"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <s v="Vick"/>
+    <s v="Brandon"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="18"/>
+    <s v="Blake"/>
+    <s v="Brian"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="18"/>
+    <s v="Walsh"/>
+    <s v="Jim"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <s v="Debolt"/>
+    <s v="Richard"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <s v="Orcutt"/>
+    <s v="Ed"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="20"/>
+    <s v="Ortiz-Self"/>
+    <s v="Lillian"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="20"/>
+    <s v="Peterson"/>
+    <s v="Strom"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="21"/>
+    <s v="Doglio"/>
+    <s v="Beth"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="21"/>
+    <s v="Dolan"/>
+    <s v="Laurie"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="22"/>
+    <s v="Appleton"/>
+    <s v="Sherry"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="22"/>
+    <s v="Hansen"/>
+    <s v="Drew"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="23"/>
+    <s v="Chapman"/>
+    <s v="Mike"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="23"/>
+    <s v="Tharinger"/>
+    <s v="Steve"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="24"/>
+    <s v="Chambers"/>
+    <s v="Kelly"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="24"/>
+    <s v="Gildon"/>
+    <s v="Chris"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="25"/>
+    <s v="Caldier"/>
+    <s v="Michelle"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="25"/>
+    <s v="Young"/>
+    <s v="Jesse"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="26"/>
+    <s v="Fey"/>
+    <s v="Jake"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="26"/>
+    <s v="Jinkins"/>
+    <s v="Laurie"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="27"/>
+    <s v="Kilduff"/>
+    <s v="Christine"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="27"/>
+    <s v="Leavitt"/>
+    <s v="Mari"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="28"/>
+    <s v="Kirby"/>
+    <s v="Steve"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="28"/>
+    <s v="Morgan"/>
+    <s v="Melanie"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="29"/>
+    <s v="Johnson"/>
+    <s v="Jesse"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="29"/>
+    <s v="Pellicciotti"/>
+    <s v="Mike"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="30"/>
+    <s v="Irwin"/>
+    <s v="Morgan"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="30"/>
+    <s v="Stokesbary"/>
+    <s v="Drew"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="31"/>
+    <s v="Davis"/>
+    <s v="Lauren"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="31"/>
+    <s v="Ryu"/>
+    <s v="Cindy"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="32"/>
+    <s v="Gregerson"/>
+    <s v="Mia"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="32"/>
+    <s v="Orwall"/>
+    <s v="Tina"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="33"/>
+    <s v="Cody"/>
+    <s v="Eileen"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="33"/>
+    <s v="Fitzgibbon"/>
+    <s v="Joe"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="34"/>
+    <s v="Griffey"/>
+    <s v="Dan"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="34"/>
+    <s v="MacEwen"/>
+    <s v="Drew"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="35"/>
+    <s v="Frame"/>
+    <s v="Noel"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="35"/>
+    <s v="Tarleton"/>
+    <s v="Gael"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="36"/>
+    <s v="Pettigrew"/>
+    <s v="Eric"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="36"/>
+    <s v="Santos"/>
+    <s v="Sharon"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="37"/>
+    <s v="Robinson"/>
+    <s v="June"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="37"/>
+    <s v="Sells"/>
+    <s v="Mike"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="38"/>
+    <s v="Eslick"/>
+    <s v="Carolyn"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="38"/>
+    <s v="Sutherland"/>
+    <s v="Robert"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="39"/>
+    <s v="Lekanoff"/>
+    <s v="Debra"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="39"/>
+    <s v="Ramel"/>
+    <s v="Alex"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="40"/>
+    <s v="Senn"/>
+    <s v="Tana"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="40"/>
+    <s v="Thai"/>
+    <s v="My-Linh"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="41"/>
+    <s v="Shewmake"/>
+    <s v="Sharon"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="41"/>
+    <s v="Van Werven"/>
+    <s v="Luanne"/>
+    <s v="R"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="42"/>
+    <s v="Chopp"/>
+    <s v="Frank"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="42"/>
+    <s v="Macri"/>
+    <s v="Nicole"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="43"/>
+    <s v="Lovick"/>
+    <s v="John"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="43"/>
+    <s v="Mead"/>
+    <s v="Jared"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="44"/>
+    <s v="Goodman"/>
+    <s v="Roger"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="44"/>
+    <s v="Springer"/>
+    <s v="Larry"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="45"/>
+    <s v="Pollet"/>
+    <s v="Gerry"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="45"/>
+    <s v="Valdez"/>
+    <s v="Javier"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="46"/>
+    <s v="Entenman"/>
+    <s v="Debra"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="46"/>
+    <s v="Sullivan"/>
+    <s v="Pat"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="47"/>
+    <s v="Slatter"/>
+    <s v="Vandana"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="47"/>
+    <s v="Walen"/>
+    <s v="Amy"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="48"/>
+    <s v="Stonier"/>
+    <s v="Monica"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="48"/>
+    <s v="Wylie"/>
+    <s v="Sharon"/>
+    <s v="D"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="49"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{13644256-95B6-4A73-A57F-2E7B4EE89857}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{13644256-95B6-4A73-A57F-2E7B4EE89857}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:F55" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
@@ -2002,6 +3118,267 @@
     </i>
     <i>
       <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Vote" fld="4" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{76D8F67A-AB6A-4E29-AB22-645C6863B743}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:E55" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="51">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="51">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="29"/>
+    </i>
+    <i>
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="32"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="34"/>
+    </i>
+    <i>
+      <x v="35"/>
+    </i>
+    <i>
+      <x v="36"/>
+    </i>
+    <i>
+      <x v="37"/>
+    </i>
+    <i>
+      <x v="38"/>
+    </i>
+    <i>
+      <x v="39"/>
+    </i>
+    <i>
+      <x v="40"/>
+    </i>
+    <i>
+      <x v="41"/>
+    </i>
+    <i>
+      <x v="42"/>
+    </i>
+    <i>
+      <x v="43"/>
+    </i>
+    <i>
+      <x v="44"/>
+    </i>
+    <i>
+      <x v="45"/>
+    </i>
+    <i>
+      <x v="46"/>
+    </i>
+    <i>
+      <x v="47"/>
+    </i>
+    <i>
+      <x v="48"/>
+    </i>
+    <i>
+      <x v="49"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="4"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
     </i>
     <i t="grand">
       <x/>
@@ -5336,15 +6713,15 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>272</v>
       </c>
       <c r="B4" t="s">
@@ -5364,16 +6741,13 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
         <v>1</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2">
-        <v>2</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2">
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="F5">
         <v>2</v>
       </c>
       <c r="G5" t="str" cm="1">
@@ -5389,16 +6763,13 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A6" s="4">
-        <v>2</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2">
-        <v>2</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2">
+      <c r="A6" s="3">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="F6">
         <v>2</v>
       </c>
       <c r="G6" t="str" cm="1">
@@ -5414,16 +6785,13 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A7" s="4">
+      <c r="A7" s="3">
         <v>3</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2">
-        <v>2</v>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2">
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="F7">
         <v>2</v>
       </c>
       <c r="G7" t="str" cm="1">
@@ -5439,16 +6807,13 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A8" s="4">
+      <c r="A8" s="3">
         <v>4</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2">
-        <v>2</v>
-      </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2">
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="F8">
         <v>2</v>
       </c>
       <c r="G8" t="str" cm="1">
@@ -5464,16 +6829,13 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9" s="4">
+      <c r="A9" s="3">
         <v>5</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2">
-        <v>2</v>
-      </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2">
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="F9">
         <v>2</v>
       </c>
       <c r="G9" t="str" cm="1">
@@ -5489,16 +6851,13 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10" s="4">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2">
-        <v>2</v>
-      </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2">
+      <c r="A10" s="3">
+        <v>6</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="F10">
         <v>2</v>
       </c>
       <c r="G10" t="str" cm="1">
@@ -5514,16 +6873,13 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A11" s="4">
-        <v>7</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2">
-        <v>2</v>
-      </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2">
+      <c r="A11" s="3">
+        <v>7</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="F11">
         <v>2</v>
       </c>
       <c r="G11" t="str" cm="1">
@@ -5539,16 +6895,13 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A12" s="4">
+      <c r="A12" s="3">
         <v>8</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2">
-        <v>2</v>
-      </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2">
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="F12">
         <v>2</v>
       </c>
       <c r="G12" t="str" cm="1">
@@ -5564,16 +6917,13 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A13" s="4">
+      <c r="A13" s="3">
         <v>9</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2">
-        <v>2</v>
-      </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2">
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="F13">
         <v>2</v>
       </c>
       <c r="G13" t="str" cm="1">
@@ -5589,16 +6939,13 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A14" s="4">
-        <v>10</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2">
-        <v>2</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2">
+      <c r="A14" s="3">
+        <v>10</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="F14">
         <v>2</v>
       </c>
       <c r="G14" t="str" cm="1">
@@ -5614,16 +6961,13 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A15" s="4">
+      <c r="A15" s="3">
         <v>11</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2">
-        <v>2</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2">
+      <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="F15">
         <v>2</v>
       </c>
       <c r="G15" t="str" cm="1">
@@ -5639,16 +6983,13 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A16" s="4">
+      <c r="A16" s="3">
         <v>12</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2">
-        <v>2</v>
-      </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2">
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="F16">
         <v>2</v>
       </c>
       <c r="G16" t="str" cm="1">
@@ -5664,18 +7005,16 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A17" s="4">
+      <c r="A17" s="3">
         <v>13</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17">
         <v>1</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17">
         <v>1</v>
       </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2">
+      <c r="F17">
         <v>2</v>
       </c>
       <c r="G17" t="str" cm="1">
@@ -5691,16 +7030,13 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A18" s="4">
+      <c r="A18" s="3">
         <v>14</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2">
-        <v>2</v>
-      </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2">
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="F18">
         <v>2</v>
       </c>
       <c r="G18" t="str" cm="1">
@@ -5716,16 +7052,13 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A19" s="4">
+      <c r="A19" s="3">
         <v>15</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2">
-        <v>2</v>
-      </c>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2">
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="F19">
         <v>2</v>
       </c>
       <c r="G19" t="str" cm="1">
@@ -5741,16 +7074,13 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A20" s="4">
+      <c r="A20" s="3">
         <v>16</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2">
-        <v>2</v>
-      </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2">
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="F20">
         <v>2</v>
       </c>
       <c r="G20" t="str" cm="1">
@@ -5766,16 +7096,13 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A21" s="4">
+      <c r="A21" s="3">
         <v>17</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2">
-        <v>2</v>
-      </c>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2">
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="F21">
         <v>2</v>
       </c>
       <c r="G21" t="str" cm="1">
@@ -5791,16 +7118,13 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A22" s="4">
+      <c r="A22" s="3">
         <v>18</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2">
-        <v>2</v>
-      </c>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2">
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="F22">
         <v>2</v>
       </c>
       <c r="G22" t="str" cm="1">
@@ -5816,16 +7140,13 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A23" s="4">
+      <c r="A23" s="3">
         <v>19</v>
       </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2">
-        <v>2</v>
-      </c>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2">
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="F23">
         <v>2</v>
       </c>
       <c r="G23" t="str" cm="1">
@@ -5841,16 +7162,13 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A24" s="4">
+      <c r="A24" s="3">
         <v>20</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2">
-        <v>2</v>
-      </c>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2">
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="F24">
         <v>2</v>
       </c>
       <c r="G24" t="str" cm="1">
@@ -5866,16 +7184,13 @@
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A25" s="4">
+      <c r="A25" s="3">
         <v>21</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2">
-        <v>2</v>
-      </c>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2">
+      <c r="D25">
+        <v>2</v>
+      </c>
+      <c r="F25">
         <v>2</v>
       </c>
       <c r="G25" t="str" cm="1">
@@ -5891,16 +7206,13 @@
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A26" s="4">
+      <c r="A26" s="3">
         <v>22</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2">
-        <v>2</v>
-      </c>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2">
+      <c r="D26">
+        <v>2</v>
+      </c>
+      <c r="F26">
         <v>2</v>
       </c>
       <c r="G26" t="str" cm="1">
@@ -5916,16 +7228,13 @@
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A27" s="4">
+      <c r="A27" s="3">
         <v>23</v>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2">
-        <v>2</v>
-      </c>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2">
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="F27">
         <v>2</v>
       </c>
       <c r="G27" t="str" cm="1">
@@ -5941,18 +7250,16 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A28" s="4">
+      <c r="A28" s="3">
         <v>24</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28">
         <v>1</v>
       </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2">
+      <c r="D28">
         <v>1</v>
       </c>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2">
+      <c r="F28">
         <v>2</v>
       </c>
       <c r="G28" t="str" cm="1">
@@ -5968,16 +7275,13 @@
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A29" s="4">
+      <c r="A29" s="3">
         <v>25</v>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2">
-        <v>2</v>
-      </c>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2">
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="F29">
         <v>2</v>
       </c>
       <c r="G29" t="str" cm="1">
@@ -5993,16 +7297,13 @@
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A30" s="4">
+      <c r="A30" s="3">
         <v>26</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2">
-        <v>2</v>
-      </c>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2">
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="F30">
         <v>2</v>
       </c>
       <c r="G30" t="str" cm="1">
@@ -6018,16 +7319,13 @@
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A31" s="4">
+      <c r="A31" s="3">
         <v>27</v>
       </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2">
-        <v>2</v>
-      </c>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2">
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="F31">
         <v>2</v>
       </c>
       <c r="G31" t="str" cm="1">
@@ -6043,16 +7341,13 @@
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A32" s="4">
+      <c r="A32" s="3">
         <v>28</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2">
-        <v>2</v>
-      </c>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2">
+      <c r="D32">
+        <v>2</v>
+      </c>
+      <c r="F32">
         <v>2</v>
       </c>
       <c r="G32" t="str" cm="1">
@@ -6068,16 +7363,13 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A33" s="4">
+      <c r="A33" s="3">
         <v>29</v>
       </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2">
-        <v>2</v>
-      </c>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2">
+      <c r="D33">
+        <v>2</v>
+      </c>
+      <c r="F33">
         <v>2</v>
       </c>
       <c r="G33" t="str" cm="1">
@@ -6093,16 +7385,13 @@
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A34" s="4">
+      <c r="A34" s="3">
         <v>30</v>
       </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2">
-        <v>2</v>
-      </c>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2">
+      <c r="D34">
+        <v>2</v>
+      </c>
+      <c r="F34">
         <v>2</v>
       </c>
       <c r="G34" t="str" cm="1">
@@ -6118,16 +7407,13 @@
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A35" s="4">
+      <c r="A35" s="3">
         <v>31</v>
       </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2">
-        <v>2</v>
-      </c>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2">
+      <c r="C35">
+        <v>2</v>
+      </c>
+      <c r="F35">
         <v>2</v>
       </c>
       <c r="G35" t="str" cm="1">
@@ -6143,16 +7429,13 @@
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A36" s="4">
+      <c r="A36" s="3">
         <v>32</v>
       </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2">
-        <v>2</v>
-      </c>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2">
+      <c r="D36">
+        <v>2</v>
+      </c>
+      <c r="F36">
         <v>2</v>
       </c>
       <c r="G36" t="str" cm="1">
@@ -6168,16 +7451,13 @@
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A37" s="4">
+      <c r="A37" s="3">
         <v>33</v>
       </c>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2">
-        <v>2</v>
-      </c>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2">
+      <c r="D37">
+        <v>2</v>
+      </c>
+      <c r="F37">
         <v>2</v>
       </c>
       <c r="G37" t="str" cm="1">
@@ -6193,16 +7473,13 @@
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A38" s="4">
+      <c r="A38" s="3">
         <v>34</v>
       </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2">
-        <v>2</v>
-      </c>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2">
+      <c r="D38">
+        <v>2</v>
+      </c>
+      <c r="F38">
         <v>2</v>
       </c>
       <c r="G38" t="str" cm="1">
@@ -6218,16 +7495,13 @@
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A39" s="4">
+      <c r="A39" s="3">
         <v>35</v>
       </c>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2">
-        <v>2</v>
-      </c>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2">
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="F39">
         <v>2</v>
       </c>
       <c r="G39" t="str" cm="1">
@@ -6243,16 +7517,13 @@
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A40" s="4">
+      <c r="A40" s="3">
         <v>36</v>
       </c>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2">
-        <v>2</v>
-      </c>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2">
+      <c r="D40">
+        <v>2</v>
+      </c>
+      <c r="F40">
         <v>2</v>
       </c>
       <c r="G40" t="str" cm="1">
@@ -6268,16 +7539,13 @@
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A41" s="4">
+      <c r="A41" s="3">
         <v>37</v>
       </c>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2">
-        <v>2</v>
-      </c>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2">
+      <c r="D41">
+        <v>2</v>
+      </c>
+      <c r="F41">
         <v>2</v>
       </c>
       <c r="G41" t="str" cm="1">
@@ -6293,16 +7561,13 @@
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A42" s="4">
+      <c r="A42" s="3">
         <v>38</v>
       </c>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2">
-        <v>2</v>
-      </c>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2">
+      <c r="D42">
+        <v>2</v>
+      </c>
+      <c r="F42">
         <v>2</v>
       </c>
       <c r="G42" t="str" cm="1">
@@ -6318,16 +7583,13 @@
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A43" s="4">
+      <c r="A43" s="3">
         <v>39</v>
       </c>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2">
-        <v>2</v>
-      </c>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2">
+      <c r="D43">
+        <v>2</v>
+      </c>
+      <c r="F43">
         <v>2</v>
       </c>
       <c r="G43" t="str" cm="1">
@@ -6343,16 +7605,13 @@
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A44" s="4">
+      <c r="A44" s="3">
         <v>40</v>
       </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2">
-        <v>2</v>
-      </c>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2">
+      <c r="D44">
+        <v>2</v>
+      </c>
+      <c r="F44">
         <v>2</v>
       </c>
       <c r="G44" t="str" cm="1">
@@ -6368,16 +7627,13 @@
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A45" s="4">
+      <c r="A45" s="3">
         <v>41</v>
       </c>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2">
-        <v>2</v>
-      </c>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2">
+      <c r="D45">
+        <v>2</v>
+      </c>
+      <c r="F45">
         <v>2</v>
       </c>
       <c r="G45" t="str" cm="1">
@@ -6393,18 +7649,16 @@
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A46" s="4">
+      <c r="A46" s="3">
         <v>42</v>
       </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2">
+      <c r="C46">
         <v>1</v>
       </c>
-      <c r="D46" s="2">
+      <c r="D46">
         <v>1</v>
       </c>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2">
+      <c r="F46">
         <v>2</v>
       </c>
       <c r="G46" t="str" cm="1">
@@ -6420,16 +7674,13 @@
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A47" s="4">
+      <c r="A47" s="3">
         <v>43</v>
       </c>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2">
-        <v>2</v>
-      </c>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2">
+      <c r="D47">
+        <v>2</v>
+      </c>
+      <c r="F47">
         <v>2</v>
       </c>
       <c r="G47" t="str" cm="1">
@@ -6445,16 +7696,13 @@
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A48" s="4">
+      <c r="A48" s="3">
         <v>44</v>
       </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2">
-        <v>2</v>
-      </c>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2">
+      <c r="D48">
+        <v>2</v>
+      </c>
+      <c r="F48">
         <v>2</v>
       </c>
       <c r="G48" t="str" cm="1">
@@ -6470,16 +7718,13 @@
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A49" s="4">
+      <c r="A49" s="3">
         <v>45</v>
       </c>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2">
-        <v>2</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2">
+      <c r="D49">
+        <v>2</v>
+      </c>
+      <c r="F49">
         <v>2</v>
       </c>
       <c r="G49" t="str" cm="1">
@@ -6495,16 +7740,13 @@
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A50" s="4">
+      <c r="A50" s="3">
         <v>46</v>
       </c>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2">
-        <v>2</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2">
+      <c r="D50">
+        <v>2</v>
+      </c>
+      <c r="F50">
         <v>2</v>
       </c>
       <c r="G50" t="str" cm="1">
@@ -6520,16 +7762,13 @@
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A51" s="4">
+      <c r="A51" s="3">
         <v>47</v>
       </c>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2">
-        <v>2</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2">
+      <c r="D51">
+        <v>2</v>
+      </c>
+      <c r="F51">
         <v>2</v>
       </c>
       <c r="G51" t="str" cm="1">
@@ -6545,18 +7784,16 @@
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A52" s="4">
+      <c r="A52" s="3">
         <v>48</v>
       </c>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2">
+      <c r="C52">
         <v>1</v>
       </c>
-      <c r="D52" s="2">
+      <c r="D52">
         <v>1</v>
       </c>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2">
+      <c r="F52">
         <v>2</v>
       </c>
       <c r="G52" t="str" cm="1">
@@ -6572,16 +7809,13 @@
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A53" s="4">
+      <c r="A53" s="3">
         <v>49</v>
       </c>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2">
-        <v>2</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2">
+      <c r="D53">
+        <v>2</v>
+      </c>
+      <c r="F53">
         <v>2</v>
       </c>
       <c r="G53" t="str" cm="1">
@@ -6597,30 +7831,4257 @@
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="B55" s="2">
-        <v>2</v>
-      </c>
-      <c r="C55" s="2">
+      <c r="B55">
+        <v>2</v>
+      </c>
+      <c r="C55">
         <v>39</v>
       </c>
-      <c r="D55" s="2">
+      <c r="D55">
         <v>57</v>
       </c>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2">
+      <c r="F55">
+        <v>98</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A3B489D-B282-403B-BB82-ABC928B979F6}">
+  <dimension ref="A1:E99"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="6.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.9296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.06640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" s="7">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" s="7">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="7">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" s="7">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" s="7">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" s="7">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9" s="7">
+        <v>4</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A10" s="7">
+        <v>5</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A11" s="7">
+        <v>5</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A12" s="7">
+        <v>6</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A13" s="7">
+        <v>6</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A14" s="7">
+        <v>7</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A15" s="7">
+        <v>7</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A16" s="7">
+        <v>8</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A17" s="7">
+        <v>8</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A18" s="7">
+        <v>9</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A19" s="7">
+        <v>9</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A20" s="7">
+        <v>10</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A21" s="7">
+        <v>10</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A22" s="7">
+        <v>11</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A23" s="7">
+        <v>11</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A24" s="7">
+        <v>12</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A25" s="7">
+        <v>12</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A26" s="7">
+        <v>13</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A27" s="7">
+        <v>13</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A28" s="7">
+        <v>14</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A29" s="7">
+        <v>14</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A30" s="7">
+        <v>15</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A31" s="7">
+        <v>15</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A32" s="7">
+        <v>16</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A33" s="7">
+        <v>16</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A34" s="7">
+        <v>17</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A35" s="7">
+        <v>17</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A36" s="7">
+        <v>18</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A37" s="7">
+        <v>18</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A38" s="7">
+        <v>19</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A39" s="7">
+        <v>19</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A40" s="7">
+        <v>20</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A41" s="7">
+        <v>20</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A42" s="7">
+        <v>21</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A43" s="7">
+        <v>21</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A44" s="7">
+        <v>22</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A45" s="7">
+        <v>22</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A46" s="7">
+        <v>23</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A47" s="7">
+        <v>23</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A48" s="7">
+        <v>24</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A49" s="7">
+        <v>24</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A50" s="7">
+        <v>25</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A51" s="7">
+        <v>25</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A52" s="7">
+        <v>26</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A53" s="7">
+        <v>26</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A54" s="7">
+        <v>27</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A55" s="7">
+        <v>27</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A56" s="7">
+        <v>28</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A57" s="7">
+        <v>28</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A58" s="7">
+        <v>29</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A59" s="7">
+        <v>29</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A60" s="7">
+        <v>30</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A61" s="7">
+        <v>30</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A62" s="7">
+        <v>31</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A63" s="7">
+        <v>31</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A64" s="7">
+        <v>32</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A65" s="7">
+        <v>32</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A66" s="7">
+        <v>33</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A67" s="7">
+        <v>33</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A68" s="7">
+        <v>34</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A69" s="7">
+        <v>34</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A70" s="7">
+        <v>35</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E70" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A71" s="7">
+        <v>35</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E71" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A72" s="7">
+        <v>36</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A73" s="7">
+        <v>36</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A74" s="7">
+        <v>37</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A75" s="7">
+        <v>37</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A76" s="7">
+        <v>38</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A77" s="7">
+        <v>38</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A78" s="7">
+        <v>39</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E78" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A79" s="7">
+        <v>39</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E79" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A80" s="7">
+        <v>40</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A81" s="7">
+        <v>40</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A82" s="7">
+        <v>41</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A83" s="7">
+        <v>41</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A84" s="7">
+        <v>42</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A85" s="7">
+        <v>42</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E85" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A86" s="7">
+        <v>43</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A87" s="7">
+        <v>43</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E87" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A88" s="7">
+        <v>44</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A89" s="7">
+        <v>44</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E89" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A90" s="7">
+        <v>45</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A91" s="7">
+        <v>45</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E91" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A92" s="7">
+        <v>46</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E92" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A93" s="7">
+        <v>46</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A94" s="7">
+        <v>47</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A95" s="7">
+        <v>47</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A96" s="7">
+        <v>48</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A97" s="7">
+        <v>48</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A98" s="7">
+        <v>49</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A99" s="7">
+        <v>49</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFB6685D-0FA5-4253-BFF5-F3D672EAAA83}">
+  <dimension ref="A1:B50"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="6.46484375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.53125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>281</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E75FA80E-623D-4E89-9C13-139BB4EE6319}">
+  <dimension ref="A1:E50"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="6.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.86328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" s="7">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="7">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" s="7">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" s="7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" s="7">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9" s="7">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A10" s="7">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A11" s="7">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A12" s="7">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A13" s="7">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A14" s="7">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A15" s="7">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A16" s="7">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A17" s="7">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A18" s="7">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A19" s="7">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A20" s="7">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A21" s="7">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A22" s="7">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A23" s="7">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A24" s="7">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A25" s="7">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A26" s="7">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A27" s="7">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A28" s="7">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A29" s="7">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A30" s="7">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A31" s="7">
+        <v>30</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A32" s="7">
+        <v>31</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A33" s="7">
+        <v>32</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A34" s="7">
+        <v>33</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A35" s="7">
+        <v>34</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A36" s="7">
+        <v>35</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A37" s="7">
+        <v>36</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A38" s="7">
+        <v>37</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A39" s="7">
+        <v>38</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A40" s="7">
+        <v>39</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A41" s="7">
+        <v>40</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A42" s="7">
+        <v>41</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A43" s="7">
+        <v>42</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A44" s="7">
+        <v>43</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A45" s="7">
+        <v>44</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A46" s="7">
+        <v>45</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A47" s="7">
+        <v>46</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A48" s="7">
+        <v>47</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A49" s="7">
+        <v>48</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A50" s="7">
+        <v>49</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6CF6B0B-B6A5-4C48-A540-4D3E90143927}">
+  <dimension ref="A3:F55"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="11.9296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.73046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.86328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>273</v>
+      </c>
+      <c r="E4" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" s="3">
+        <v>1</v>
+      </c>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10">
+        <v>2</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10">
+        <v>2</v>
+      </c>
+      <c r="F5" t="str" cm="1">
+        <f t="array" ref="F5">_xlfn.IFS(
+C5=2,"2 Yea",
+B5=2,"2 Nay",
+AND(C5=1,B5=1),"1 Yea 1 Nay",
+AND(A5=1,C5=1),"1 Yea 1 No Vote",
+AND(B5=1,A5=1),"1 Nay 1 No Vote",
+A5=2,"2 No Vote"
+)</f>
+        <v>2 Yea</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" s="3">
+        <v>2</v>
+      </c>
+      <c r="B6" s="10">
+        <v>2</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10">
+        <v>2</v>
+      </c>
+      <c r="F6" t="str" cm="1">
+        <f t="array" ref="F6">_xlfn.IFS(
+C6=2,"2 Yea",
+B6=2,"2 Nay",
+AND(C6=1,B6=1),"1 Yea 1 Nay",
+AND(A6=1,C6=1),"1 Yea 1 No Vote",
+AND(B6=1,A6=1),"1 Nay 1 No Vote",
+A6=2,"2 No Vote"
+)</f>
+        <v>2 Nay</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" s="3">
+        <v>3</v>
+      </c>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10">
+        <v>2</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10">
+        <v>2</v>
+      </c>
+      <c r="F7" t="str" cm="1">
+        <f t="array" ref="F7">_xlfn.IFS(
+C7=2,"2 Yea",
+B7=2,"2 Nay",
+AND(C7=1,B7=1),"1 Yea 1 Nay",
+AND(A7=1,C7=1),"1 Yea 1 No Vote",
+AND(B7=1,A7=1),"1 Nay 1 No Vote",
+A7=2,"2 No Vote"
+)</f>
+        <v>2 Yea</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" s="3">
+        <v>4</v>
+      </c>
+      <c r="B8" s="10">
+        <v>2</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10">
+        <v>2</v>
+      </c>
+      <c r="F8" t="str" cm="1">
+        <f t="array" ref="F8">_xlfn.IFS(
+C8=2,"2 Yea",
+B8=2,"2 Nay",
+AND(C8=1,B8=1),"1 Yea 1 Nay",
+AND(A8=1,C8=1),"1 Yea 1 No Vote",
+AND(B8=1,A8=1),"1 Nay 1 No Vote",
+A8=2,"2 No Vote"
+)</f>
+        <v>2 Nay</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" s="3">
+        <v>5</v>
+      </c>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10">
+        <v>2</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10">
+        <v>2</v>
+      </c>
+      <c r="F9" t="str" cm="1">
+        <f t="array" ref="F9">_xlfn.IFS(
+C9=2,"2 Yea",
+B9=2,"2 Nay",
+AND(C9=1,B9=1),"1 Yea 1 Nay",
+AND(A9=1,C9=1),"1 Yea 1 No Vote",
+AND(B9=1,A9=1),"1 Nay 1 No Vote",
+A9=2,"2 No Vote"
+)</f>
+        <v>2 Yea</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A10" s="3">
+        <v>6</v>
+      </c>
+      <c r="B10" s="10">
+        <v>2</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10">
+        <v>2</v>
+      </c>
+      <c r="F10" t="str" cm="1">
+        <f t="array" ref="F10">_xlfn.IFS(
+C10=2,"2 Yea",
+B10=2,"2 Nay",
+AND(C10=1,B10=1),"1 Yea 1 Nay",
+AND(A10=1,C10=1),"1 Yea 1 No Vote",
+AND(B10=1,A10=1),"1 Nay 1 No Vote",
+A10=2,"2 No Vote"
+)</f>
+        <v>2 Nay</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A11" s="3">
+        <v>7</v>
+      </c>
+      <c r="B11" s="10">
+        <v>2</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10">
+        <v>2</v>
+      </c>
+      <c r="F11" t="str" cm="1">
+        <f t="array" ref="F11">_xlfn.IFS(
+C11=2,"2 Yea",
+B11=2,"2 Nay",
+AND(C11=1,B11=1),"1 Yea 1 Nay",
+AND(A11=1,C11=1),"1 Yea 1 No Vote",
+AND(B11=1,A11=1),"1 Nay 1 No Vote",
+A11=2,"2 No Vote"
+)</f>
+        <v>2 Nay</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A12" s="3">
+        <v>8</v>
+      </c>
+      <c r="B12" s="10">
+        <v>2</v>
+      </c>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10">
+        <v>2</v>
+      </c>
+      <c r="F12" t="str" cm="1">
+        <f t="array" ref="F12">_xlfn.IFS(
+C12=2,"2 Yea",
+B12=2,"2 Nay",
+AND(C12=1,B12=1),"1 Yea 1 Nay",
+AND(A12=1,C12=1),"1 Yea 1 No Vote",
+AND(B12=1,A12=1),"1 Nay 1 No Vote",
+A12=2,"2 No Vote"
+)</f>
+        <v>2 Nay</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A13" s="3">
+        <v>9</v>
+      </c>
+      <c r="B13" s="10">
+        <v>2</v>
+      </c>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10">
+        <v>2</v>
+      </c>
+      <c r="F13" t="str" cm="1">
+        <f t="array" ref="F13">_xlfn.IFS(
+C13=2,"2 Yea",
+B13=2,"2 Nay",
+AND(C13=1,B13=1),"1 Yea 1 Nay",
+AND(A13=1,C13=1),"1 Yea 1 No Vote",
+AND(B13=1,A13=1),"1 Nay 1 No Vote",
+A13=2,"2 No Vote"
+)</f>
+        <v>2 Nay</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A14" s="3">
+        <v>10</v>
+      </c>
+      <c r="B14" s="10">
+        <v>1</v>
+      </c>
+      <c r="C14" s="10">
+        <v>1</v>
+      </c>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10">
+        <v>2</v>
+      </c>
+      <c r="F14" t="str" cm="1">
+        <f t="array" ref="F14">_xlfn.IFS(
+C14=2,"2 Yea",
+B14=2,"2 Nay",
+AND(C14=1,B14=1),"1 Yea 1 Nay",
+AND(A14=1,C14=1),"1 Yea 1 No Vote",
+AND(B14=1,A14=1),"1 Nay 1 No Vote",
+A14=2,"2 No Vote"
+)</f>
+        <v>1 Yea 1 Nay</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A15" s="3">
+        <v>11</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10">
+        <v>2</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10">
+        <v>2</v>
+      </c>
+      <c r="F15" t="str" cm="1">
+        <f t="array" ref="F15">_xlfn.IFS(
+C15=2,"2 Yea",
+B15=2,"2 Nay",
+AND(C15=1,B15=1),"1 Yea 1 Nay",
+AND(A15=1,C15=1),"1 Yea 1 No Vote",
+AND(B15=1,A15=1),"1 Nay 1 No Vote",
+A15=2,"2 No Vote"
+)</f>
+        <v>2 Yea</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A16" s="3">
+        <v>12</v>
+      </c>
+      <c r="B16" s="10">
+        <v>2</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10">
+        <v>2</v>
+      </c>
+      <c r="F16" t="str" cm="1">
+        <f t="array" ref="F16">_xlfn.IFS(
+C16=2,"2 Yea",
+B16=2,"2 Nay",
+AND(C16=1,B16=1),"1 Yea 1 Nay",
+AND(A16=1,C16=1),"1 Yea 1 No Vote",
+AND(B16=1,A16=1),"1 Nay 1 No Vote",
+A16=2,"2 No Vote"
+)</f>
+        <v>2 Nay</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A17" s="3">
+        <v>13</v>
+      </c>
+      <c r="B17" s="10">
+        <v>1</v>
+      </c>
+      <c r="C17" s="10">
+        <v>1</v>
+      </c>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10">
+        <v>2</v>
+      </c>
+      <c r="F17" t="str" cm="1">
+        <f t="array" ref="F17">_xlfn.IFS(
+C17=2,"2 Yea",
+B17=2,"2 Nay",
+AND(C17=1,B17=1),"1 Yea 1 Nay",
+AND(A17=1,C17=1),"1 Yea 1 No Vote",
+AND(B17=1,A17=1),"1 Nay 1 No Vote",
+A17=2,"2 No Vote"
+)</f>
+        <v>1 Yea 1 Nay</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A18" s="3">
+        <v>14</v>
+      </c>
+      <c r="B18" s="10">
+        <v>2</v>
+      </c>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10">
+        <v>2</v>
+      </c>
+      <c r="F18" t="str" cm="1">
+        <f t="array" ref="F18">_xlfn.IFS(
+C18=2,"2 Yea",
+B18=2,"2 Nay",
+AND(C18=1,B18=1),"1 Yea 1 Nay",
+AND(A18=1,C18=1),"1 Yea 1 No Vote",
+AND(B18=1,A18=1),"1 Nay 1 No Vote",
+A18=2,"2 No Vote"
+)</f>
+        <v>2 Nay</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A19" s="3">
+        <v>15</v>
+      </c>
+      <c r="B19" s="10">
+        <v>1</v>
+      </c>
+      <c r="C19" s="10">
+        <v>1</v>
+      </c>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10">
+        <v>2</v>
+      </c>
+      <c r="F19" t="str" cm="1">
+        <f t="array" ref="F19">_xlfn.IFS(
+C19=2,"2 Yea",
+B19=2,"2 Nay",
+AND(C19=1,B19=1),"1 Yea 1 Nay",
+AND(A19=1,C19=1),"1 Yea 1 No Vote",
+AND(B19=1,A19=1),"1 Nay 1 No Vote",
+A19=2,"2 No Vote"
+)</f>
+        <v>1 Yea 1 Nay</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A20" s="3">
+        <v>16</v>
+      </c>
+      <c r="B20" s="10">
+        <v>2</v>
+      </c>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10">
+        <v>2</v>
+      </c>
+      <c r="F20" t="str" cm="1">
+        <f t="array" ref="F20">_xlfn.IFS(
+C20=2,"2 Yea",
+B20=2,"2 Nay",
+AND(C20=1,B20=1),"1 Yea 1 Nay",
+AND(A20=1,C20=1),"1 Yea 1 No Vote",
+AND(B20=1,A20=1),"1 Nay 1 No Vote",
+A20=2,"2 No Vote"
+)</f>
+        <v>2 Nay</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A21" s="3">
+        <v>17</v>
+      </c>
+      <c r="B21" s="10">
+        <v>2</v>
+      </c>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10">
+        <v>2</v>
+      </c>
+      <c r="F21" t="str" cm="1">
+        <f t="array" ref="F21">_xlfn.IFS(
+C21=2,"2 Yea",
+B21=2,"2 Nay",
+AND(C21=1,B21=1),"1 Yea 1 Nay",
+AND(A21=1,C21=1),"1 Yea 1 No Vote",
+AND(B21=1,A21=1),"1 Nay 1 No Vote",
+A21=2,"2 No Vote"
+)</f>
+        <v>2 Nay</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A22" s="3">
+        <v>18</v>
+      </c>
+      <c r="B22" s="10">
+        <v>2</v>
+      </c>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10">
+        <v>2</v>
+      </c>
+      <c r="F22" t="str" cm="1">
+        <f t="array" ref="F22">_xlfn.IFS(
+C22=2,"2 Yea",
+B22=2,"2 Nay",
+AND(C22=1,B22=1),"1 Yea 1 Nay",
+AND(A22=1,C22=1),"1 Yea 1 No Vote",
+AND(B22=1,A22=1),"1 Nay 1 No Vote",
+A22=2,"2 No Vote"
+)</f>
+        <v>2 Nay</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A23" s="3">
+        <v>19</v>
+      </c>
+      <c r="B23" s="10">
+        <v>1</v>
+      </c>
+      <c r="C23" s="10">
+        <v>1</v>
+      </c>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10">
+        <v>2</v>
+      </c>
+      <c r="F23" t="str" cm="1">
+        <f t="array" ref="F23">_xlfn.IFS(
+C23=2,"2 Yea",
+B23=2,"2 Nay",
+AND(C23=1,B23=1),"1 Yea 1 Nay",
+AND(A23=1,C23=1),"1 Yea 1 No Vote",
+AND(B23=1,A23=1),"1 Nay 1 No Vote",
+A23=2,"2 No Vote"
+)</f>
+        <v>1 Yea 1 Nay</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A24" s="3">
+        <v>20</v>
+      </c>
+      <c r="B24" s="10">
+        <v>2</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10">
+        <v>2</v>
+      </c>
+      <c r="F24" t="str" cm="1">
+        <f t="array" ref="F24">_xlfn.IFS(
+C24=2,"2 Yea",
+B24=2,"2 Nay",
+AND(C24=1,B24=1),"1 Yea 1 Nay",
+AND(A24=1,C24=1),"1 Yea 1 No Vote",
+AND(B24=1,A24=1),"1 Nay 1 No Vote",
+A24=2,"2 No Vote"
+)</f>
+        <v>2 Nay</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A25" s="3">
+        <v>21</v>
+      </c>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10">
+        <v>2</v>
+      </c>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10">
+        <v>2</v>
+      </c>
+      <c r="F25" t="str" cm="1">
+        <f t="array" ref="F25">_xlfn.IFS(
+C25=2,"2 Yea",
+B25=2,"2 Nay",
+AND(C25=1,B25=1),"1 Yea 1 Nay",
+AND(A25=1,C25=1),"1 Yea 1 No Vote",
+AND(B25=1,A25=1),"1 Nay 1 No Vote",
+A25=2,"2 No Vote"
+)</f>
+        <v>2 Yea</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A26" s="3">
+        <v>22</v>
+      </c>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10">
+        <v>2</v>
+      </c>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10">
+        <v>2</v>
+      </c>
+      <c r="F26" t="str" cm="1">
+        <f t="array" ref="F26">_xlfn.IFS(
+C26=2,"2 Yea",
+B26=2,"2 Nay",
+AND(C26=1,B26=1),"1 Yea 1 Nay",
+AND(A26=1,C26=1),"1 Yea 1 No Vote",
+AND(B26=1,A26=1),"1 Nay 1 No Vote",
+A26=2,"2 No Vote"
+)</f>
+        <v>2 Yea</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A27" s="3">
+        <v>23</v>
+      </c>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10">
+        <v>2</v>
+      </c>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10">
+        <v>2</v>
+      </c>
+      <c r="F27" t="str" cm="1">
+        <f t="array" ref="F27">_xlfn.IFS(
+C27=2,"2 Yea",
+B27=2,"2 Nay",
+AND(C27=1,B27=1),"1 Yea 1 Nay",
+AND(A27=1,C27=1),"1 Yea 1 No Vote",
+AND(B27=1,A27=1),"1 Nay 1 No Vote",
+A27=2,"2 No Vote"
+)</f>
+        <v>2 Yea</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A28" s="3">
+        <v>24</v>
+      </c>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10">
+        <v>2</v>
+      </c>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10">
+        <v>2</v>
+      </c>
+      <c r="F28" t="str" cm="1">
+        <f t="array" ref="F28">_xlfn.IFS(
+C28=2,"2 Yea",
+B28=2,"2 Nay",
+AND(C28=1,B28=1),"1 Yea 1 Nay",
+AND(A28=1,C28=1),"1 Yea 1 No Vote",
+AND(B28=1,A28=1),"1 Nay 1 No Vote",
+A28=2,"2 No Vote"
+)</f>
+        <v>2 Yea</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A29" s="3">
+        <v>25</v>
+      </c>
+      <c r="B29" s="10">
+        <v>2</v>
+      </c>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10">
+        <v>2</v>
+      </c>
+      <c r="F29" t="str" cm="1">
+        <f t="array" ref="F29">_xlfn.IFS(
+C29=2,"2 Yea",
+B29=2,"2 Nay",
+AND(C29=1,B29=1),"1 Yea 1 Nay",
+AND(A29=1,C29=1),"1 Yea 1 No Vote",
+AND(B29=1,A29=1),"1 Nay 1 No Vote",
+A29=2,"2 No Vote"
+)</f>
+        <v>2 Nay</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A30" s="3">
+        <v>26</v>
+      </c>
+      <c r="B30" s="10">
+        <v>2</v>
+      </c>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10">
+        <v>2</v>
+      </c>
+      <c r="F30" t="str" cm="1">
+        <f t="array" ref="F30">_xlfn.IFS(
+C30=2,"2 Yea",
+B30=2,"2 Nay",
+AND(C30=1,B30=1),"1 Yea 1 Nay",
+AND(A30=1,C30=1),"1 Yea 1 No Vote",
+AND(B30=1,A30=1),"1 Nay 1 No Vote",
+A30=2,"2 No Vote"
+)</f>
+        <v>2 Nay</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A31" s="3">
+        <v>27</v>
+      </c>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10">
+        <v>2</v>
+      </c>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10">
+        <v>2</v>
+      </c>
+      <c r="F31" t="str" cm="1">
+        <f t="array" ref="F31">_xlfn.IFS(
+C31=2,"2 Yea",
+B31=2,"2 Nay",
+AND(C31=1,B31=1),"1 Yea 1 Nay",
+AND(A31=1,C31=1),"1 Yea 1 No Vote",
+AND(B31=1,A31=1),"1 Nay 1 No Vote",
+A31=2,"2 No Vote"
+)</f>
+        <v>2 Yea</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A32" s="3">
+        <v>28</v>
+      </c>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10">
+        <v>2</v>
+      </c>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10">
+        <v>2</v>
+      </c>
+      <c r="F32" t="str" cm="1">
+        <f t="array" ref="F32">_xlfn.IFS(
+C32=2,"2 Yea",
+B32=2,"2 Nay",
+AND(C32=1,B32=1),"1 Yea 1 Nay",
+AND(A32=1,C32=1),"1 Yea 1 No Vote",
+AND(B32=1,A32=1),"1 Nay 1 No Vote",
+A32=2,"2 No Vote"
+)</f>
+        <v>2 Yea</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A33" s="3">
+        <v>29</v>
+      </c>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10">
+        <v>2</v>
+      </c>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10">
+        <v>2</v>
+      </c>
+      <c r="F33" t="str" cm="1">
+        <f t="array" ref="F33">_xlfn.IFS(
+C33=2,"2 Yea",
+B33=2,"2 Nay",
+AND(C33=1,B33=1),"1 Yea 1 Nay",
+AND(A33=1,C33=1),"1 Yea 1 No Vote",
+AND(B33=1,A33=1),"1 Nay 1 No Vote",
+A33=2,"2 No Vote"
+)</f>
+        <v>2 Yea</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A34" s="3">
+        <v>30</v>
+      </c>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10">
+        <v>2</v>
+      </c>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10">
+        <v>2</v>
+      </c>
+      <c r="F34" t="str" cm="1">
+        <f t="array" ref="F34">_xlfn.IFS(
+C34=2,"2 Yea",
+B34=2,"2 Nay",
+AND(C34=1,B34=1),"1 Yea 1 Nay",
+AND(A34=1,C34=1),"1 Yea 1 No Vote",
+AND(B34=1,A34=1),"1 Nay 1 No Vote",
+A34=2,"2 No Vote"
+)</f>
+        <v>2 Yea</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A35" s="3">
+        <v>31</v>
+      </c>
+      <c r="B35" s="10">
+        <v>2</v>
+      </c>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10">
+        <v>2</v>
+      </c>
+      <c r="F35" t="str" cm="1">
+        <f t="array" ref="F35">_xlfn.IFS(
+C35=2,"2 Yea",
+B35=2,"2 Nay",
+AND(C35=1,B35=1),"1 Yea 1 Nay",
+AND(A35=1,C35=1),"1 Yea 1 No Vote",
+AND(B35=1,A35=1),"1 Nay 1 No Vote",
+A35=2,"2 No Vote"
+)</f>
+        <v>2 Nay</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A36" s="3">
+        <v>32</v>
+      </c>
+      <c r="B36" s="10"/>
+      <c r="C36" s="10">
+        <v>2</v>
+      </c>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10">
+        <v>2</v>
+      </c>
+      <c r="F36" t="str" cm="1">
+        <f t="array" ref="F36">_xlfn.IFS(
+C36=2,"2 Yea",
+B36=2,"2 Nay",
+AND(C36=1,B36=1),"1 Yea 1 Nay",
+AND(A36=1,C36=1),"1 Yea 1 No Vote",
+AND(B36=1,A36=1),"1 Nay 1 No Vote",
+A36=2,"2 No Vote"
+)</f>
+        <v>2 Yea</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A37" s="3">
+        <v>33</v>
+      </c>
+      <c r="B37" s="10"/>
+      <c r="C37" s="10">
+        <v>2</v>
+      </c>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10">
+        <v>2</v>
+      </c>
+      <c r="F37" t="str" cm="1">
+        <f t="array" ref="F37">_xlfn.IFS(
+C37=2,"2 Yea",
+B37=2,"2 Nay",
+AND(C37=1,B37=1),"1 Yea 1 Nay",
+AND(A37=1,C37=1),"1 Yea 1 No Vote",
+AND(B37=1,A37=1),"1 Nay 1 No Vote",
+A37=2,"2 No Vote"
+)</f>
+        <v>2 Yea</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A38" s="3">
+        <v>34</v>
+      </c>
+      <c r="B38" s="10"/>
+      <c r="C38" s="10">
+        <v>2</v>
+      </c>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10">
+        <v>2</v>
+      </c>
+      <c r="F38" t="str" cm="1">
+        <f t="array" ref="F38">_xlfn.IFS(
+C38=2,"2 Yea",
+B38=2,"2 Nay",
+AND(C38=1,B38=1),"1 Yea 1 Nay",
+AND(A38=1,C38=1),"1 Yea 1 No Vote",
+AND(B38=1,A38=1),"1 Nay 1 No Vote",
+A38=2,"2 No Vote"
+)</f>
+        <v>2 Yea</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A39" s="3">
+        <v>35</v>
+      </c>
+      <c r="B39" s="10">
+        <v>2</v>
+      </c>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10">
+        <v>2</v>
+      </c>
+      <c r="F39" t="str" cm="1">
+        <f t="array" ref="F39">_xlfn.IFS(
+C39=2,"2 Yea",
+B39=2,"2 Nay",
+AND(C39=1,B39=1),"1 Yea 1 Nay",
+AND(A39=1,C39=1),"1 Yea 1 No Vote",
+AND(B39=1,A39=1),"1 Nay 1 No Vote",
+A39=2,"2 No Vote"
+)</f>
+        <v>2 Nay</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A40" s="3">
+        <v>36</v>
+      </c>
+      <c r="B40" s="10"/>
+      <c r="C40" s="10">
+        <v>2</v>
+      </c>
+      <c r="D40" s="10"/>
+      <c r="E40" s="10">
+        <v>2</v>
+      </c>
+      <c r="F40" t="str" cm="1">
+        <f t="array" ref="F40">_xlfn.IFS(
+C40=2,"2 Yea",
+B40=2,"2 Nay",
+AND(C40=1,B40=1),"1 Yea 1 Nay",
+AND(A40=1,C40=1),"1 Yea 1 No Vote",
+AND(B40=1,A40=1),"1 Nay 1 No Vote",
+A40=2,"2 No Vote"
+)</f>
+        <v>2 Yea</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A41" s="3">
+        <v>37</v>
+      </c>
+      <c r="B41" s="10"/>
+      <c r="C41" s="10">
+        <v>2</v>
+      </c>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10">
+        <v>2</v>
+      </c>
+      <c r="F41" t="str" cm="1">
+        <f t="array" ref="F41">_xlfn.IFS(
+C41=2,"2 Yea",
+B41=2,"2 Nay",
+AND(C41=1,B41=1),"1 Yea 1 Nay",
+AND(A41=1,C41=1),"1 Yea 1 No Vote",
+AND(B41=1,A41=1),"1 Nay 1 No Vote",
+A41=2,"2 No Vote"
+)</f>
+        <v>2 Yea</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A42" s="3">
+        <v>38</v>
+      </c>
+      <c r="B42" s="10"/>
+      <c r="C42" s="10">
+        <v>2</v>
+      </c>
+      <c r="D42" s="10"/>
+      <c r="E42" s="10">
+        <v>2</v>
+      </c>
+      <c r="F42" t="str" cm="1">
+        <f t="array" ref="F42">_xlfn.IFS(
+C42=2,"2 Yea",
+B42=2,"2 Nay",
+AND(C42=1,B42=1),"1 Yea 1 Nay",
+AND(A42=1,C42=1),"1 Yea 1 No Vote",
+AND(B42=1,A42=1),"1 Nay 1 No Vote",
+A42=2,"2 No Vote"
+)</f>
+        <v>2 Yea</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A43" s="3">
+        <v>39</v>
+      </c>
+      <c r="B43" s="10">
+        <v>2</v>
+      </c>
+      <c r="C43" s="10"/>
+      <c r="D43" s="10"/>
+      <c r="E43" s="10">
+        <v>2</v>
+      </c>
+      <c r="F43" t="str" cm="1">
+        <f t="array" ref="F43">_xlfn.IFS(
+C43=2,"2 Yea",
+B43=2,"2 Nay",
+AND(C43=1,B43=1),"1 Yea 1 Nay",
+AND(A43=1,C43=1),"1 Yea 1 No Vote",
+AND(B43=1,A43=1),"1 Nay 1 No Vote",
+A43=2,"2 No Vote"
+)</f>
+        <v>2 Nay</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A44" s="3">
+        <v>40</v>
+      </c>
+      <c r="B44" s="10"/>
+      <c r="C44" s="10">
+        <v>2</v>
+      </c>
+      <c r="D44" s="10"/>
+      <c r="E44" s="10">
+        <v>2</v>
+      </c>
+      <c r="F44" t="str" cm="1">
+        <f t="array" ref="F44">_xlfn.IFS(
+C44=2,"2 Yea",
+B44=2,"2 Nay",
+AND(C44=1,B44=1),"1 Yea 1 Nay",
+AND(A44=1,C44=1),"1 Yea 1 No Vote",
+AND(B44=1,A44=1),"1 Nay 1 No Vote",
+A44=2,"2 No Vote"
+)</f>
+        <v>2 Yea</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A45" s="3">
+        <v>41</v>
+      </c>
+      <c r="B45" s="10"/>
+      <c r="C45" s="10">
+        <v>2</v>
+      </c>
+      <c r="D45" s="10"/>
+      <c r="E45" s="10">
+        <v>2</v>
+      </c>
+      <c r="F45" t="str" cm="1">
+        <f t="array" ref="F45">_xlfn.IFS(
+C45=2,"2 Yea",
+B45=2,"2 Nay",
+AND(C45=1,B45=1),"1 Yea 1 Nay",
+AND(A45=1,C45=1),"1 Yea 1 No Vote",
+AND(B45=1,A45=1),"1 Nay 1 No Vote",
+A45=2,"2 No Vote"
+)</f>
+        <v>2 Yea</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A46" s="3">
+        <v>42</v>
+      </c>
+      <c r="B46" s="10">
+        <v>1</v>
+      </c>
+      <c r="C46" s="10">
+        <v>1</v>
+      </c>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10">
+        <v>2</v>
+      </c>
+      <c r="F46" t="str" cm="1">
+        <f t="array" ref="F46">_xlfn.IFS(
+C46=2,"2 Yea",
+B46=2,"2 Nay",
+AND(C46=1,B46=1),"1 Yea 1 Nay",
+AND(A46=1,C46=1),"1 Yea 1 No Vote",
+AND(B46=1,A46=1),"1 Nay 1 No Vote",
+A46=2,"2 No Vote"
+)</f>
+        <v>1 Yea 1 Nay</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A47" s="3">
+        <v>43</v>
+      </c>
+      <c r="B47" s="10"/>
+      <c r="C47" s="10">
+        <v>2</v>
+      </c>
+      <c r="D47" s="10"/>
+      <c r="E47" s="10">
+        <v>2</v>
+      </c>
+      <c r="F47" t="str" cm="1">
+        <f t="array" ref="F47">_xlfn.IFS(
+C47=2,"2 Yea",
+B47=2,"2 Nay",
+AND(C47=1,B47=1),"1 Yea 1 Nay",
+AND(A47=1,C47=1),"1 Yea 1 No Vote",
+AND(B47=1,A47=1),"1 Nay 1 No Vote",
+A47=2,"2 No Vote"
+)</f>
+        <v>2 Yea</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A48" s="3">
+        <v>44</v>
+      </c>
+      <c r="B48" s="10"/>
+      <c r="C48" s="10">
+        <v>2</v>
+      </c>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10">
+        <v>2</v>
+      </c>
+      <c r="F48" t="str" cm="1">
+        <f t="array" ref="F48">_xlfn.IFS(
+C48=2,"2 Yea",
+B48=2,"2 Nay",
+AND(C48=1,B48=1),"1 Yea 1 Nay",
+AND(A48=1,C48=1),"1 Yea 1 No Vote",
+AND(B48=1,A48=1),"1 Nay 1 No Vote",
+A48=2,"2 No Vote"
+)</f>
+        <v>2 Yea</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A49" s="3">
+        <v>45</v>
+      </c>
+      <c r="B49" s="10"/>
+      <c r="C49" s="10">
+        <v>2</v>
+      </c>
+      <c r="D49" s="10"/>
+      <c r="E49" s="10">
+        <v>2</v>
+      </c>
+      <c r="F49" t="str" cm="1">
+        <f t="array" ref="F49">_xlfn.IFS(
+C49=2,"2 Yea",
+B49=2,"2 Nay",
+AND(C49=1,B49=1),"1 Yea 1 Nay",
+AND(A49=1,C49=1),"1 Yea 1 No Vote",
+AND(B49=1,A49=1),"1 Nay 1 No Vote",
+A49=2,"2 No Vote"
+)</f>
+        <v>2 Yea</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A50" s="3">
+        <v>46</v>
+      </c>
+      <c r="B50" s="10"/>
+      <c r="C50" s="10">
+        <v>2</v>
+      </c>
+      <c r="D50" s="10"/>
+      <c r="E50" s="10">
+        <v>2</v>
+      </c>
+      <c r="F50" t="str" cm="1">
+        <f t="array" ref="F50">_xlfn.IFS(
+C50=2,"2 Yea",
+B50=2,"2 Nay",
+AND(C50=1,B50=1),"1 Yea 1 Nay",
+AND(A50=1,C50=1),"1 Yea 1 No Vote",
+AND(B50=1,A50=1),"1 Nay 1 No Vote",
+A50=2,"2 No Vote"
+)</f>
+        <v>2 Yea</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A51" s="3">
+        <v>47</v>
+      </c>
+      <c r="B51" s="10"/>
+      <c r="C51" s="10">
+        <v>2</v>
+      </c>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10">
+        <v>2</v>
+      </c>
+      <c r="F51" t="str" cm="1">
+        <f t="array" ref="F51">_xlfn.IFS(
+C51=2,"2 Yea",
+B51=2,"2 Nay",
+AND(C51=1,B51=1),"1 Yea 1 Nay",
+AND(A51=1,C51=1),"1 Yea 1 No Vote",
+AND(B51=1,A51=1),"1 Nay 1 No Vote",
+A51=2,"2 No Vote"
+)</f>
+        <v>2 Yea</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A52" s="3">
+        <v>48</v>
+      </c>
+      <c r="B52" s="10"/>
+      <c r="C52" s="10">
+        <v>2</v>
+      </c>
+      <c r="D52" s="10"/>
+      <c r="E52" s="10">
+        <v>2</v>
+      </c>
+      <c r="F52" t="str" cm="1">
+        <f t="array" ref="F52">_xlfn.IFS(
+C52=2,"2 Yea",
+B52=2,"2 Nay",
+AND(C52=1,B52=1),"1 Yea 1 Nay",
+AND(A52=1,C52=1),"1 Yea 1 No Vote",
+AND(B52=1,A52=1),"1 Nay 1 No Vote",
+A52=2,"2 No Vote"
+)</f>
+        <v>2 Yea</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A53" s="3">
+        <v>49</v>
+      </c>
+      <c r="B53" s="10"/>
+      <c r="C53" s="10">
+        <v>2</v>
+      </c>
+      <c r="D53" s="10"/>
+      <c r="E53" s="10">
+        <v>2</v>
+      </c>
+      <c r="F53" t="str" cm="1">
+        <f t="array" ref="F53">_xlfn.IFS(
+C53=2,"2 Yea",
+B53=2,"2 Nay",
+AND(C53=1,B53=1),"1 Yea 1 Nay",
+AND(A53=1,C53=1),"1 Yea 1 No Vote",
+AND(B53=1,A53=1),"1 Nay 1 No Vote",
+A53=2,"2 No Vote"
+)</f>
+        <v>2 Yea</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A54" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B54" s="10"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A55" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B55" s="10">
+        <v>39</v>
+      </c>
+      <c r="C55" s="10">
+        <v>59</v>
+      </c>
+      <c r="D55" s="10"/>
+      <c r="E55" s="10">
         <v>98</v>
       </c>
     </row>
